--- a/data/trans_camb/P14B23-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Habitat-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,27</t>
+          <t>-1,47; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,86</t>
+          <t>1,75; 6,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,68</t>
+          <t>-4,36; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,07</t>
+          <t>-5,44; -0,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,13</t>
+          <t>-2,28; 1,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,27</t>
+          <t>-1,16; 2,17</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 104,74</t>
+          <t>-57,96; 116,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,36; 424,42</t>
+          <t>56,07; 452,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 23,26</t>
+          <t>-39,44; 26,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -1,14</t>
+          <t>-51,05; -2,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 24,78</t>
+          <t>-35,64; 21,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 49,38</t>
+          <t>-18,74; 47,67</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,05</t>
+          <t>-2,66; 0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,73</t>
+          <t>-2,66; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,2</t>
+          <t>-4,63; 0,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,18</t>
+          <t>-3,15; 1,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,3</t>
+          <t>-2,95; -0,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,23</t>
+          <t>-2,84; 0,25</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,55; 4,99</t>
+          <t>-72,34; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 32,72</t>
+          <t>-68,47; 40,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 2,64</t>
+          <t>-48,11; 3,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 17,97</t>
+          <t>-32,58; 20,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -5,61</t>
+          <t>-46,43; -6,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 3,77</t>
+          <t>-47,78; 4,39</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,84</t>
+          <t>-1,68; 1,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,18</t>
+          <t>-0,72; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,25</t>
+          <t>-3,11; 2,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 3,36</t>
+          <t>-5,02; 3,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,4</t>
+          <t>-1,7; 1,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,56</t>
+          <t>-1,37; 2,66</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 153,38</t>
+          <t>-52,2; 138,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 243,99</t>
+          <t>-27,16; 270,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 36,7</t>
+          <t>-35,42; 39,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 52,27</t>
+          <t>-57,0; 46,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 37,38</t>
+          <t>-30,63; 34,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 60,75</t>
+          <t>-24,98; 63,03</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,84</t>
+          <t>-1,98; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,33</t>
+          <t>-0,08; 3,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,7</t>
+          <t>-3,65; 1,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,08</t>
+          <t>-2,37; 2,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,4</t>
+          <t>-2,47; 0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,44</t>
+          <t>-0,66; 2,37</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 46,65</t>
+          <t>-56,97; 51,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 166,29</t>
+          <t>-3,64; 158,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 11,05</t>
+          <t>-41,62; 16,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 31,86</t>
+          <t>-26,82; 37,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,59; 9,14</t>
+          <t>-40,42; 7,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 51,55</t>
+          <t>-10,71; 50,49</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,25</t>
+          <t>-1,23; 0,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,1</t>
+          <t>0,14; 2,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,05</t>
+          <t>-2,66; -0,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,45</t>
+          <t>-2,43; 0,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,15</t>
+          <t>-1,74; -0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,0</t>
+          <t>-0,68; 1,07</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 13,37</t>
+          <t>-43,33; 13,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,49; 99,1</t>
+          <t>4,66; 95,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -0,58</t>
+          <t>-30,63; -1,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 6,4</t>
+          <t>-28,27; 5,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -3,12</t>
+          <t>-30,04; -4,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 20,39</t>
+          <t>-11,83; 21,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P14B23-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,38</t>
+          <t>-1,55; 1,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,07</t>
+          <t>1,49; 5,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,85</t>
+          <t>-3,93; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,19</t>
+          <t>-5,44; -0,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,03</t>
+          <t>-2,25; 1,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,17</t>
+          <t>-0,97; 2,58</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>186,21%</t>
+          <t>184,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-30,78%</t>
+          <t>-25,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 116,93</t>
+          <t>-59,61; 109,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,07; 452,17</t>
+          <t>41,46; 446,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 26,41</t>
+          <t>-37,91; 34,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -2,98</t>
+          <t>-47,17; 0,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 21,29</t>
+          <t>-35,23; 24,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 47,67</t>
+          <t>-15,64; 55,94</t>
         </is>
       </c>
     </row>
@@ -754,27 +754,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-1,08</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-1,63</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,1</t>
+          <t>-2,63; -0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,86</t>
+          <t>-1,97; 1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,21</t>
+          <t>-4,47; 0,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,36</t>
+          <t>-3,14; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,42</t>
+          <t>-2,97; -0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,25</t>
+          <t>-2,01; 0,61</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-25,1%</t>
+          <t>-12,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-11,77%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,43%</t>
+          <t>-12,81%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,34; 6,98</t>
+          <t>-70,33; -1,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 40,02</t>
+          <t>-50,67; 47,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 3,74</t>
+          <t>-47,9; 4,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 20,48</t>
+          <t>-32,18; 19,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; -6,73</t>
+          <t>-48,68; -5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 4,39</t>
+          <t>-31,34; 12,52</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,93</t>
+          <t>-1,5; 1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,59</t>
+          <t>-0,74; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,33</t>
+          <t>-3,11; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,02</t>
+          <t>-0,09; 4,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,4</t>
+          <t>-1,64; 1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,66</t>
+          <t>0,15; 3,43</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 138,06</t>
+          <t>-53,86; 159,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 270,89</t>
+          <t>-25,83; 255,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 39,82</t>
+          <t>-35,96; 38,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,0; 46,08</t>
+          <t>-1,1; 82,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 34,87</t>
+          <t>-29,66; 35,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 63,03</t>
+          <t>2,29; 85,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,83</t>
+          <t>-1,99; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,19</t>
+          <t>0,12; 3,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,04</t>
+          <t>-3,77; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,47</t>
+          <t>-1,51; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,34</t>
+          <t>-2,37; 0,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,37</t>
+          <t>-0,24; 2,54</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 51,03</t>
+          <t>-56,94; 42,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 158,57</t>
+          <t>-1,21; 186,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 16,44</t>
+          <t>-42,17; 16,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 37,54</t>
+          <t>-16,99; 48,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 7,19</t>
+          <t>-39,15; 8,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 50,49</t>
+          <t>-4,21; 54,52</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,29</t>
+          <t>-1,39; 0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,1</t>
+          <t>0,46; 2,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,08</t>
+          <t>-2,63; -0,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,39</t>
+          <t>-1,31; 1,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,25</t>
+          <t>-1,6; -0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,07</t>
+          <t>-0,12; 1,39</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-0,31%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 13,85</t>
+          <t>-45,85; 9,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,66; 95,98</t>
+          <t>16,14; 106,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -1,05</t>
+          <t>-30,25; -0,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 5,49</t>
+          <t>-15,2; 16,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,04; -4,63</t>
+          <t>-28,7; -4,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 21,51</t>
+          <t>-2,14; 28,15</t>
         </is>
       </c>
     </row>
